--- a/calculations/D38999_26AXXXX_Dimensions.xlsx
+++ b/calculations/D38999_26AXXXX_Dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lelem\git_repositories\projects\D38999-3MF\calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1516BB6A-23B3-48F6-8A83-4022DCD8A1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0742377-26B7-42F7-8255-F8C68AA24260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{58E9E39D-3151-410B-8DC1-39983DB63DF0}"/>
+    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{58E9E39D-3151-410B-8DC1-39983DB63DF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -467,12 +467,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -811,6 +810,34 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.578125" customWidth="1"/>
+    <col min="2" max="3" width="28.3671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.15625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.1015625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.20703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.47265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.9453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.26171875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.26171875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.9453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.9453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.83984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.9453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.68359375" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="26.62890625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.1015625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="28.3671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.83984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="37.15625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="31.1015625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="28.1015625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.9453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="28.47265625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29.9453125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.47265625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="27.05078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.55000000000000004">
@@ -888,25 +915,25 @@
       <c r="W2" t="s">
         <v>116</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" t="s">
         <v>104</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" t="s">
         <v>34</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2" t="s">
         <v>43</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AA2" t="s">
         <v>44</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AB2" t="s">
         <v>40</v>
       </c>
-      <c r="AC2" s="4" t="s">
+      <c r="AC2" t="s">
         <v>36</v>
       </c>
-      <c r="AD2" s="4" t="s">
+      <c r="AD2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -980,25 +1007,25 @@
       <c r="W3">
         <v>1.32</v>
       </c>
-      <c r="X3" s="4">
+      <c r="X3">
         <v>10</v>
       </c>
-      <c r="Y3" s="4">
+      <c r="Y3">
         <v>0.5</v>
       </c>
-      <c r="Z3" s="4">
+      <c r="Z3">
         <v>1</v>
       </c>
-      <c r="AA3" s="4">
+      <c r="AA3">
         <v>5</v>
       </c>
-      <c r="AB3" s="4">
+      <c r="AB3">
         <v>5</v>
       </c>
-      <c r="AC3" s="4">
+      <c r="AC3">
         <v>4</v>
       </c>
-      <c r="AD3" s="4">
+      <c r="AD3">
         <v>31</v>
       </c>
     </row>

--- a/calculations/D38999_26AXXXX_Dimensions.xlsx
+++ b/calculations/D38999_26AXXXX_Dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lelem\git_repositories\projects\D38999-3MF\calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0742377-26B7-42F7-8255-F8C68AA24260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A036BF-89D3-4E7D-9307-182D7C6C6AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{58E9E39D-3151-410B-8DC1-39983DB63DF0}"/>
+    <workbookView xWindow="29805" yWindow="-16200" windowWidth="14010" windowHeight="15585" xr2:uid="{58E9E39D-3151-410B-8DC1-39983DB63DF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="135">
   <si>
     <t>A</t>
   </si>
@@ -420,13 +420,34 @@
   </si>
   <si>
     <t>26AJ</t>
+  </si>
+  <si>
+    <t>Accessory thread major diameter</t>
+  </si>
+  <si>
+    <t>accessory thread minor diameter</t>
+  </si>
+  <si>
+    <t>accessory thread pitch</t>
+  </si>
+  <si>
+    <t>coupling nut thread offset</t>
+  </si>
+  <si>
+    <t>coupling nut groove half angle</t>
+  </si>
+  <si>
+    <t>detent groove height</t>
+  </si>
+  <si>
+    <t>detent ridge height</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -806,8 +827,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15FAAE9F-A0B2-467B-96FA-D5BCA8B98733}">
-  <dimension ref="A1:AH111"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:AP111"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.578125" customWidth="1"/>
     <col min="2" max="3" width="28.3671875" bestFit="1" customWidth="1"/>
@@ -838,14 +859,16 @@
     <col min="29" max="29" width="29.9453125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="18.47265625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="27.05078125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="26.3671875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="26.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -936,8 +959,23 @@
       <c r="AD2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AE2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1028,13 +1066,28 @@
       <c r="AD3">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AE3">
+        <v>2.16</v>
+      </c>
+      <c r="AF3">
+        <v>15</v>
+      </c>
+      <c r="AG3">
+        <v>0.4</v>
+      </c>
+      <c r="AH3">
+        <v>0.3</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1128,8 +1181,14 @@
       <c r="AE6" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35">
       <c r="A8" t="s">
         <v>119</v>
       </c>
@@ -1225,8 +1284,14 @@
       <c r="AE8">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF8" s="1">
+        <v>11.794</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>10.557</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35">
       <c r="A9" t="s">
         <v>120</v>
       </c>
@@ -1322,8 +1387,14 @@
       <c r="AE9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF9" s="1">
+        <v>14.794</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>13.557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35">
       <c r="A10" t="s">
         <v>121</v>
       </c>
@@ -1419,8 +1490,14 @@
       <c r="AE10">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF10" s="1">
+        <v>17.794</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>16.556999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35">
       <c r="A11" t="s">
         <v>122</v>
       </c>
@@ -1516,8 +1593,14 @@
       <c r="AE11">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF11" s="1">
+        <v>21.794</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>20.556999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35">
       <c r="A12" t="s">
         <v>123</v>
       </c>
@@ -1613,8 +1696,14 @@
       <c r="AE12">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF12" s="1">
+        <v>24.794</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>23.55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
       <c r="A13" t="s">
         <v>124</v>
       </c>
@@ -1710,8 +1799,14 @@
       <c r="AE13">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF13" s="1">
+        <v>27.794</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>26.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35">
       <c r="A14" t="s">
         <v>125</v>
       </c>
@@ -1807,8 +1902,14 @@
       <c r="AE14">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF14" s="1">
+        <v>30.794</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>29.55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35">
       <c r="A15" t="s">
         <v>126</v>
       </c>
@@ -1904,8 +2005,14 @@
       <c r="AE15">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF15" s="1">
+        <v>33.793999999999997</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>32.549999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -2001,13 +2108,19 @@
       <c r="AE16">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF16" s="1">
+        <v>36.793999999999997</v>
+      </c>
+      <c r="AG16" s="1">
+        <v>35.549999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:42">
       <c r="A18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:42">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2024,7 +2137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:42">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -2041,10 +2154,10 @@
         <v>265</v>
       </c>
       <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
-      <c r="AG21" s="1"/>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AO21" s="1"/>
+      <c r="AP21" s="1"/>
+    </row>
+    <row r="22" spans="1:42">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -2061,10 +2174,10 @@
         <v>320</v>
       </c>
       <c r="AE22" s="1"/>
-      <c r="AF22" s="1"/>
-      <c r="AG22" s="1"/>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AO22" s="1"/>
+      <c r="AP22" s="1"/>
+    </row>
+    <row r="23" spans="1:42">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -2081,10 +2194,10 @@
         <v>312</v>
       </c>
       <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AO23" s="1"/>
+      <c r="AP23" s="1"/>
+    </row>
+    <row r="24" spans="1:42">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -2101,10 +2214,10 @@
         <v>275</v>
       </c>
       <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1"/>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AO24" s="1"/>
+      <c r="AP24" s="1"/>
+    </row>
+    <row r="25" spans="1:42">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -2124,7 +2237,7 @@
       <c r="AF25" s="1"/>
       <c r="AG25" s="1"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:42">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -2144,7 +2257,7 @@
       <c r="AF26" s="1"/>
       <c r="AG26" s="1"/>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:42">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -2164,7 +2277,7 @@
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:42">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -2184,7 +2297,7 @@
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:42">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -2204,7 +2317,7 @@
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:42">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -2221,7 +2334,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:42">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -2238,7 +2351,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:42">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -2258,7 +2371,7 @@
       <c r="AF32" s="1"/>
       <c r="AH32" s="1"/>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:34">
       <c r="A33" t="s">
         <v>71</v>
       </c>
@@ -2278,7 +2391,7 @@
       <c r="AF33" s="1"/>
       <c r="AH33" s="1"/>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:34">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -2298,7 +2411,7 @@
       <c r="AF34" s="1"/>
       <c r="AH34" s="1"/>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:34">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -2318,7 +2431,7 @@
       <c r="AF35" s="1"/>
       <c r="AH35" s="1"/>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:34">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -2339,7 +2452,7 @@
       <c r="AF36" s="1"/>
       <c r="AH36" s="1"/>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:34">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -2359,7 +2472,7 @@
       <c r="AF37" s="1"/>
       <c r="AH37" s="1"/>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:34">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -2379,7 +2492,7 @@
       <c r="AF38" s="1"/>
       <c r="AH38" s="1"/>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:34">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -2399,7 +2512,7 @@
       <c r="AF39" s="1"/>
       <c r="AH39" s="1"/>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:34">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -2419,7 +2532,7 @@
       <c r="AF40" s="1"/>
       <c r="AH40" s="1"/>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:34">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -2436,7 +2549,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:34">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -2453,7 +2566,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:34">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -2470,7 +2583,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:34">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2487,12 +2600,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:34">
       <c r="A46" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:34">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -2503,7 +2616,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>0</v>
       </c>
@@ -2514,7 +2627,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2525,7 +2638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>1</v>
       </c>
@@ -2536,7 +2649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>2</v>
       </c>
@@ -2547,7 +2660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -2558,7 +2671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -2569,7 +2682,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -2580,7 +2693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -2591,7 +2704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -2602,7 +2715,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -2610,7 +2723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -2618,12 +2731,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2643,7 +2756,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -2663,7 +2776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -2683,7 +2796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
         <v>1</v>
       </c>
@@ -2703,7 +2816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2723,7 +2836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -2743,7 +2856,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -2763,7 +2876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -2783,7 +2896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -2803,7 +2916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -2823,17 +2936,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:14">
       <c r="A74">
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -2862,7 +2975,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -2892,7 +3005,7 @@
       </c>
       <c r="N76" s="1"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2922,7 +3035,7 @@
       </c>
       <c r="N77" s="1"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
         <v>1</v>
       </c>
@@ -2952,7 +3065,7 @@
       </c>
       <c r="N78" s="1"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
         <v>2</v>
       </c>
@@ -2982,7 +3095,7 @@
       </c>
       <c r="N79" s="1"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
         <v>3</v>
       </c>
@@ -3012,7 +3125,7 @@
       </c>
       <c r="N80" s="1"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -3042,7 +3155,7 @@
       </c>
       <c r="N81" s="1"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
         <v>7</v>
       </c>
@@ -3072,7 +3185,7 @@
       </c>
       <c r="N82" s="1"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -3102,7 +3215,7 @@
       </c>
       <c r="N83" s="1"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -3132,12 +3245,12 @@
       </c>
       <c r="N84" s="1"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -3145,7 +3258,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
         <v>0</v>
       </c>
@@ -3153,7 +3266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -3161,7 +3274,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>1</v>
       </c>
@@ -3169,7 +3282,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
         <v>2</v>
       </c>
@@ -3177,7 +3290,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
         <v>3</v>
       </c>
@@ -3185,7 +3298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:14">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -3193,7 +3306,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:14">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -3201,7 +3314,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:10">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -3209,7 +3322,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:10">
       <c r="A98" t="s">
         <v>9</v>
       </c>
@@ -3217,17 +3330,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:10">
       <c r="A100" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:10">
       <c r="A101">
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:10">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -3259,7 +3372,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:10">
       <c r="A103" t="s">
         <v>0</v>
       </c>
@@ -3293,7 +3406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:10">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -3327,7 +3440,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:10">
       <c r="A105" t="s">
         <v>1</v>
       </c>
@@ -3361,7 +3474,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:10">
       <c r="A106" t="s">
         <v>2</v>
       </c>
@@ -3395,7 +3508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:10">
       <c r="A107" t="s">
         <v>3</v>
       </c>
@@ -3429,7 +3542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:10">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -3463,7 +3576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:10">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -3497,7 +3610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:10">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -3531,7 +3644,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:10">
       <c r="A111" t="s">
         <v>9</v>
       </c>
